--- a/branches/hiv-patient_fhir-182/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/branches/hiv-patient_fhir-182/StructureDefinition-hiv-patient-is-new.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2187" uniqueCount="477">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2188" uniqueCount="477">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T17:19:03+00:00</t>
+    <t>2023-05-05T18:22:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -658,7 +658,21 @@
     <t>Knowing what kind of observation is being made is essential to understanding the observation.</t>
   </si>
   <si>
-    <t>http://openhie.org/fhir/rwanda-hiv/ValueSet/vs-is-patient-new</t>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="http://snomed.info/sct"/&gt;
+    &lt;code value="769681006"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
+    <t>example</t>
+  </si>
+  <si>
+    <t>Codes identifying names of simple observations.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/observation-codes</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -1098,9 +1112,6 @@
   <si>
     <t>Only used if not implicit in code found in Observation.code.  In many systems, this may be represented as a related observation instead of an inline component.   
 If the use case requires BodySite to be handled as a separate resource (e.g. to identify and track separately) then use the standard extension[ bodySite](http://hl7.org/fhir/R4/extension-bodysite.html).</t>
-  </si>
-  <si>
-    <t>example</t>
   </si>
   <si>
     <t>Codes describing anatomical locations. May include laterality.</t>
@@ -1457,12 +1468,6 @@
   </si>
   <si>
     <t>*All* code-value and  component.code-component.value pairs need to be taken into account to correctly understand the meaning of the observation.</t>
-  </si>
-  <si>
-    <t>Codes identifying names of simple observations.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-codes</t>
   </si>
   <si>
     <t>&lt; 363787002 |Observable entity| OR @@ -1852,7 +1857,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="63.70703125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="57.43359375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="50.40625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
@@ -3732,7 +3737,7 @@
         <v>82</v>
       </c>
       <c r="S16" t="s" s="2">
-        <v>82</v>
+        <v>206</v>
       </c>
       <c r="T16" t="s" s="2">
         <v>82</v>
@@ -3747,11 +3752,13 @@
         <v>82</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="Y16" s="2"/>
+        <v>207</v>
+      </c>
+      <c r="Y16" t="s" s="2">
+        <v>208</v>
+      </c>
       <c r="Z16" t="s" s="2">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>82</v>
@@ -3784,30 +3791,30 @@
         <v>104</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="AP16" t="s" s="2">
-        <v>212</v>
+        <v>215</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3830,13 +3837,13 @@
         <v>82</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -3887,7 +3894,7 @@
         <v>82</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
@@ -3911,7 +3918,7 @@
         <v>82</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>82</v>
@@ -3922,10 +3929,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3954,7 +3961,7 @@
         <v>139</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="N18" t="s" s="2">
         <v>141</v>
@@ -3995,19 +4002,19 @@
         <v>82</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
@@ -4031,7 +4038,7 @@
         <v>82</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>82</v>
@@ -4042,10 +4049,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4068,19 +4075,19 @@
         <v>93</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>82</v>
@@ -4129,7 +4136,7 @@
         <v>82</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -4150,10 +4157,10 @@
         <v>82</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>82</v>
@@ -4164,10 +4171,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4190,19 +4197,19 @@
         <v>93</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>82</v>
@@ -4212,7 +4219,7 @@
         <v>82</v>
       </c>
       <c r="S20" t="s" s="2">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="T20" t="s" s="2">
         <v>82</v>
@@ -4251,7 +4258,7 @@
         <v>82</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -4272,10 +4279,10 @@
         <v>82</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>82</v>
@@ -4286,10 +4293,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4312,19 +4319,19 @@
         <v>93</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="O21" t="s" s="2">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>82</v>
@@ -4373,7 +4380,7 @@
         <v>82</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -4388,19 +4395,19 @@
         <v>104</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="AP21" t="s" s="2">
         <v>82</v>
@@ -4408,10 +4415,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4434,16 +4441,16 @@
         <v>93</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4493,7 +4500,7 @@
         <v>82</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -4514,13 +4521,13 @@
         <v>82</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="AP22" t="s" s="2">
         <v>82</v>
@@ -4528,14 +4535,14 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
@@ -4554,19 +4561,19 @@
         <v>93</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="O23" t="s" s="2">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>82</v>
@@ -4615,7 +4622,7 @@
         <v>82</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -4630,19 +4637,19 @@
         <v>104</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="AP23" t="s" s="2">
         <v>82</v>
@@ -4650,14 +4657,14 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -4676,19 +4683,19 @@
         <v>93</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>82</v>
@@ -4737,7 +4744,7 @@
         <v>82</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -4752,19 +4759,19 @@
         <v>104</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="AP24" t="s" s="2">
         <v>82</v>
@@ -4772,10 +4779,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4798,16 +4805,16 @@
         <v>93</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -4857,7 +4864,7 @@
         <v>82</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -4878,13 +4885,13 @@
         <v>82</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="AP25" t="s" s="2">
         <v>82</v>
@@ -4892,10 +4899,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4918,17 +4925,17 @@
         <v>93</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" t="s" s="2">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>82</v>
@@ -4977,7 +4984,7 @@
         <v>82</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -4992,19 +4999,19 @@
         <v>104</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="AL26" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="AP26" t="s" s="2">
         <v>82</v>
@@ -5012,10 +5019,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5038,19 +5045,19 @@
         <v>93</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>82</v>
@@ -5087,17 +5094,17 @@
         <v>82</v>
       </c>
       <c r="AB27" t="s" s="2">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="AC27" s="2"/>
       <c r="AD27" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -5106,7 +5113,7 @@
         <v>92</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AJ27" t="s" s="2">
         <v>104</v>
@@ -5115,30 +5122,30 @@
         <v>82</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>310</v>
+        <v>313</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="C28" t="s" s="2">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="D28" t="s" s="2">
         <v>82</v>
@@ -5160,19 +5167,19 @@
         <v>93</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>82</v>
@@ -5221,7 +5228,7 @@
         <v>82</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -5230,7 +5237,7 @@
         <v>92</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AJ28" t="s" s="2">
         <v>104</v>
@@ -5239,27 +5246,27 @@
         <v>82</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>310</v>
+        <v>313</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5285,16 +5292,16 @@
         <v>191</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>82</v>
@@ -5319,13 +5326,13 @@
         <v>82</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>82</v>
@@ -5343,7 +5350,7 @@
         <v>82</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5352,7 +5359,7 @@
         <v>92</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="AJ29" t="s" s="2">
         <v>104</v>
@@ -5367,7 +5374,7 @@
         <v>135</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>82</v>
@@ -5378,14 +5385,14 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
@@ -5407,16 +5414,16 @@
         <v>191</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>82</v>
@@ -5441,13 +5448,13 @@
         <v>82</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>82</v>
@@ -5465,7 +5472,7 @@
         <v>82</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -5483,27 +5490,27 @@
         <v>82</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP30" t="s" s="2">
-        <v>334</v>
+        <v>337</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5526,19 +5533,19 @@
         <v>82</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>82</v>
@@ -5587,7 +5594,7 @@
         <v>82</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -5608,10 +5615,10 @@
         <v>82</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>82</v>
@@ -5622,10 +5629,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5651,13 +5658,13 @@
         <v>191</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5683,13 +5690,13 @@
         <v>82</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>347</v>
+        <v>207</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>82</v>
@@ -5707,7 +5714,7 @@
         <v>82</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -5725,27 +5732,27 @@
         <v>82</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5771,16 +5778,16 @@
         <v>191</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>82</v>
@@ -5805,13 +5812,13 @@
         <v>82</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>347</v>
+        <v>207</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>82</v>
@@ -5829,7 +5836,7 @@
         <v>82</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -5850,10 +5857,10 @@
         <v>82</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>82</v>
@@ -5864,10 +5871,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5890,16 +5897,16 @@
         <v>82</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -5949,7 +5956,7 @@
         <v>82</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -5967,27 +5974,27 @@
         <v>82</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6010,16 +6017,16 @@
         <v>82</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -6069,7 +6076,7 @@
         <v>82</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -6087,27 +6094,27 @@
         <v>82</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6130,19 +6137,19 @@
         <v>82</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>82</v>
@@ -6191,7 +6198,7 @@
         <v>82</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6203,7 +6210,7 @@
         <v>82</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>82</v>
@@ -6212,10 +6219,10 @@
         <v>82</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>82</v>
@@ -6226,10 +6233,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6252,13 +6259,13 @@
         <v>82</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6309,7 +6316,7 @@
         <v>82</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6333,7 +6340,7 @@
         <v>82</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>82</v>
@@ -6344,10 +6351,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6376,7 +6383,7 @@
         <v>139</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="N38" t="s" s="2">
         <v>141</v>
@@ -6429,7 +6436,7 @@
         <v>82</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6453,7 +6460,7 @@
         <v>82</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>82</v>
@@ -6464,14 +6471,14 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -6493,10 +6500,10 @@
         <v>138</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="N39" t="s" s="2">
         <v>141</v>
@@ -6551,7 +6558,7 @@
         <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -6586,10 +6593,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6612,13 +6619,13 @@
         <v>82</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6669,7 +6676,7 @@
         <v>82</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -6678,7 +6685,7 @@
         <v>92</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="AJ40" t="s" s="2">
         <v>104</v>
@@ -6690,10 +6697,10 @@
         <v>82</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>82</v>
@@ -6704,10 +6711,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6730,13 +6737,13 @@
         <v>82</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6787,7 +6794,7 @@
         <v>82</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -6796,7 +6803,7 @@
         <v>92</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="AJ41" t="s" s="2">
         <v>104</v>
@@ -6808,10 +6815,10 @@
         <v>82</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>82</v>
@@ -6822,10 +6829,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6851,16 +6858,16 @@
         <v>191</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>82</v>
@@ -6888,10 +6895,10 @@
         <v>116</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>82</v>
@@ -6909,7 +6916,7 @@
         <v>82</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -6927,13 +6934,13 @@
         <v>82</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>82</v>
@@ -6944,10 +6951,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6973,16 +6980,16 @@
         <v>191</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>82</v>
@@ -7007,13 +7014,13 @@
         <v>82</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>347</v>
+        <v>207</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>82</v>
@@ -7031,7 +7038,7 @@
         <v>82</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -7049,13 +7056,13 @@
         <v>82</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>82</v>
@@ -7066,10 +7073,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7092,17 +7099,17 @@
         <v>82</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>82</v>
@@ -7151,7 +7158,7 @@
         <v>82</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7175,7 +7182,7 @@
         <v>82</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>82</v>
@@ -7186,10 +7193,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7212,13 +7219,13 @@
         <v>82</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7269,7 +7276,7 @@
         <v>82</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7290,10 +7297,10 @@
         <v>82</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>82</v>
@@ -7304,10 +7311,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7330,16 +7337,16 @@
         <v>93</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -7389,7 +7396,7 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7410,10 +7417,10 @@
         <v>82</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>82</v>
@@ -7424,10 +7431,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7450,16 +7457,16 @@
         <v>93</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7509,7 +7516,7 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7530,10 +7537,10 @@
         <v>82</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>82</v>
@@ -7544,10 +7551,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7570,19 +7577,19 @@
         <v>93</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>82</v>
@@ -7631,7 +7638,7 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7652,10 +7659,10 @@
         <v>82</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>82</v>
@@ -7666,10 +7673,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7692,13 +7699,13 @@
         <v>82</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -7749,7 +7756,7 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -7773,7 +7780,7 @@
         <v>82</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>82</v>
@@ -7784,10 +7791,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7816,7 +7823,7 @@
         <v>139</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="N50" t="s" s="2">
         <v>141</v>
@@ -7869,7 +7876,7 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -7893,7 +7900,7 @@
         <v>82</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>82</v>
@@ -7904,14 +7911,14 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -7933,10 +7940,10 @@
         <v>138</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="N51" t="s" s="2">
         <v>141</v>
@@ -7991,7 +7998,7 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8026,10 +8033,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8055,13 +8062,13 @@
         <v>191</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="O52" t="s" s="2">
         <v>205</v>
@@ -8089,13 +8096,13 @@
         <v>82</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>347</v>
+        <v>207</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>461</v>
+        <v>208</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>462</v>
+        <v>209</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>82</v>
@@ -8113,7 +8120,7 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>92</v>
@@ -8134,13 +8141,13 @@
         <v>463</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>82</v>
@@ -8180,13 +8187,13 @@
         <v>466</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="N53" t="s" s="2">
         <v>467</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>82</v>
@@ -8256,16 +8263,16 @@
         <v>468</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>310</v>
+        <v>313</v>
       </c>
     </row>
     <row r="54" hidden="true">
@@ -8308,7 +8315,7 @@
         <v>472</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>82</v>
@@ -8333,13 +8340,13 @@
         <v>82</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>82</v>
@@ -8366,7 +8373,7 @@
         <v>92</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="AJ54" t="s" s="2">
         <v>104</v>
@@ -8381,7 +8388,7 @@
         <v>135</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>82</v>
@@ -8399,7 +8406,7 @@
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -8421,16 +8428,16 @@
         <v>191</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>82</v>
@@ -8455,13 +8462,13 @@
         <v>82</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>82</v>
@@ -8497,19 +8504,19 @@
         <v>82</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>334</v>
+        <v>337</v>
       </c>
     </row>
     <row r="56" hidden="true">
@@ -8549,10 +8556,10 @@
         <v>476</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>82</v>
@@ -8622,10 +8629,10 @@
         <v>82</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>82</v>

--- a/branches/hiv-patient_fhir-182/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/branches/hiv-patient_fhir-182/StructureDefinition-hiv-patient-is-new.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T18:22:11+00:00</t>
+    <t>2023-05-05T18:45:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/hiv-patient_fhir-182/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/branches/hiv-patient_fhir-182/StructureDefinition-hiv-patient-is-new.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T18:45:12+00:00</t>
+    <t>2023-05-05T19:04:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/hiv-patient_fhir-182/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/branches/hiv-patient_fhir-182/StructureDefinition-hiv-patient-is-new.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T19:04:07+00:00</t>
+    <t>2023-05-05T19:04:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/hiv-patient_fhir-182/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/branches/hiv-patient_fhir-182/StructureDefinition-hiv-patient-is-new.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T19:04:40+00:00</t>
+    <t>2023-05-05T20:15:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/hiv-patient_fhir-182/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/branches/hiv-patient_fhir-182/StructureDefinition-hiv-patient-is-new.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T20:15:22+00:00</t>
+    <t>2023-05-05T20:15:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/hiv-patient_fhir-182/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/branches/hiv-patient_fhir-182/StructureDefinition-hiv-patient-is-new.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T20:15:42+00:00</t>
+    <t>2023-05-05T20:23:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/hiv-patient_fhir-182/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/branches/hiv-patient_fhir-182/StructureDefinition-hiv-patient-is-new.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T20:23:19+00:00</t>
+    <t>2023-05-05T20:23:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/hiv-patient_fhir-182/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/branches/hiv-patient_fhir-182/StructureDefinition-hiv-patient-is-new.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T20:23:46+00:00</t>
+    <t>2023-05-05T20:33:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/hiv-patient_fhir-182/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/branches/hiv-patient_fhir-182/StructureDefinition-hiv-patient-is-new.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T20:33:04+00:00</t>
+    <t>2023-05-05T20:39:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/hiv-patient_fhir-182/StructureDefinition-hiv-patient-is-new.xlsx
+++ b/branches/hiv-patient_fhir-182/StructureDefinition-hiv-patient-is-new.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-05T20:39:09+00:00</t>
+    <t>2023-05-05T20:44:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
